--- a/output/spreadsheet/t01-08-物品资产主表-260928.xlsx
+++ b/output/spreadsheet/t01-08-物品资产主表-260928.xlsx
@@ -3725,7 +3725,7 @@
       </ns0:c>
       <ns0:c r="C6" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>基础攻击、状态施加、恢复、上限及灵障分别引用效果；19表补灵障模板，丹药首瓶开战就绪。</ns0:t>
+          <ns0:t>基础攻击、状态施加、恢复、上限及灵盾分别引用效果；19表补灵盾模板，丹药首瓶开战就绪。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D6" s="4" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </ns0:c>
       <ns0:c r="B16" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>灵障重复生成</ns0:t>
+          <ns0:t>灵盾重复生成</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C16" s="4" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </ns0:c>
       <ns0:c r="B17" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>灵障容量</ns0:t>
+          <ns0:t>灵盾容量</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C17" s="4" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </ns0:c>
       <ns0:c r="D17" s="6" t="inlineStr">
         <ns0:is>
-          <ns0:t>当前普通灵障上限＝境界基础上限＋阵盘、法器及其他明确来源的上限加成。凡人10、炼气20、筑基30、结丹40、元婴50、化神60；上限加成暂不设统一封顶。池内存值仍受当前上限约束。</ns0:t>
+          <ns0:t>当前普通灵盾上限＝境界基础上限＋阵盘、法器及其他明确来源的上限加成。凡人10、炼气20、筑基30、结丹40、元婴50、化神60；上限加成暂不设统一封顶。池内存值仍受当前上限约束。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E17" s="4" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </ns0:c>
       <ns0:c r="B18" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>灵障战内时限</ns0:t>
+          <ns0:t>灵盾战内时限</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C18" s="4" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </ns0:c>
       <ns0:c r="B19" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>灵障珠满值停用与重启</ns0:t>
+          <ns0:t>灵盾珠满值停用与重启</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C19" s="4" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </ns0:c>
       <ns0:c r="D19" s="6" t="inlineStr">
         <ns0:is>
-          <ns0:t>F14灵障珠在普通灵障达到当前上限时立即停用，不发动、不扣灵力、不继续CD倒数，也不积累就绪资格。停用后，受到攻击使普通灵障值减少，才重新启用，并从完整10.5秒CD重新倒数；不继承停用前剩余CD，不在受击当刻立即补盾。CD完成且正常发动资格满足时，消耗6灵力，增加min(15,容量缺口)普通灵障；若因此达到上限，再次停用。此为本件专属停用条件，不等于受到【禁用】控制，也不自动推广其他法器。</ns0:t>
+          <ns0:t>F14灵盾珠在普通灵盾达到当前上限时立即停用，不发动、不扣灵力、不继续CD倒数，也不积累就绪资格。停用后，受到攻击使普通灵盾值减少，才重新启用，并从完整10.5秒CD重新倒数；不继承停用前剩余CD，不在受击当刻立即补盾。CD完成且正常发动资格满足时，消耗6灵力，增加min(15,容量缺口)普通灵盾；若因此达到上限，再次停用。此为本件专属停用条件，不等于受到【禁用】控制，也不自动推广其他法器。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E19" s="4" t="inlineStr">
@@ -15964,12 +15964,12 @@
       </ns0:c>
       <ns0:c r="D150" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>灵障珠</ns0:t>
+          <ns0:t>灵盾珠</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E150" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>生成普通灵障</ns0:t>
+          <ns0:t>生成普通灵盾</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F150" s="4" t="n">
@@ -16003,12 +16003,12 @@
       </ns0:c>
       <ns0:c r="M150" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>01 M06 C04；19表灵障模板</ns0:t>
+          <ns0:t>01 M06 C04；19表灵盾模板</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="N150" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>CD10.5秒／灵力6；再次生成加进现有普通灵障池，实际增加不超过当前容量缺口；容量足够时10＋15＝25，溢出不存入。；战内不自然到期、不随时间衰减；剩余值保留到被消耗或战斗结束，战后清空。；F14灵障珠在普通灵障达到当前上限时立即停用，不发动、不扣灵力、不继续CD倒数，也不积累就绪资格。停用后，受到攻击使普通灵障值减少，才重新启用，并从完整10.5秒CD重新倒数；不继承停用前剩余CD，不在受击当刻立即补盾。CD完成且正常发动资格满足时，消耗6灵力，增加min(15,容量缺口)普通灵障；若因此达到上限，再次停用。此为本件专属停用条件，不等于受到【禁用】控制，也不自动推广其他法器。</ns0:t>
+          <ns0:t>CD10.5秒／灵力6；再次生成加进现有普通灵盾池，实际增加不超过当前容量缺口；容量足够时10＋15＝25，溢出不存入。；战内不自然到期、不随时间衰减；剩余值保留到被消耗或战斗结束，战后清空。；F14灵盾珠在普通灵盾达到当前上限时立即停用，不发动、不扣灵力、不继续CD倒数，也不积累就绪资格。停用后，受到攻击使普通灵盾值减少，才重新启用，并从完整10.5秒CD重新倒数；不继承停用前剩余CD，不在受击当刻立即补盾。CD完成且正常发动资格满足时，消耗6灵力，增加min(15,容量缺口)普通灵盾；若因此达到上限，再次停用。此为本件专属停用条件，不等于受到【禁用】控制，也不自动推广其他法器。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="O150" s="4" t="inlineStr">
@@ -22157,7 +22157,7 @@
       </ns0:c>
       <ns0:c r="B101" s="7" t="str">
         <ns0:f>'04_法器'!B23</ns0:f>
-        <ns0:v>灵障珠</ns0:v>
+        <ns0:v>灵盾珠</ns0:v>
       </ns0:c>
       <ns0:c r="C101" s="7" t="str">
         <ns0:f>'04_法器'!C23</ns0:f>
@@ -23333,17 +23333,17 @@
       </ns0:c>
       <ns0:c r="B13" s="15" t="inlineStr">
         <ns0:is>
-          <ns0:t>普通灵障吸收</ns0:t>
+          <ns0:t>普通灵盾吸收</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C13" s="15" t="inlineStr">
         <ns0:is>
-          <ns0:t>符合普通防御路线的伤害按30%，实际扣值min(现灵障,进入阶段伤害×30%)。</ns0:t>
+          <ns0:t>符合普通防御路线的伤害按30%，实际扣值min(现灵盾,进入阶段伤害×30%)。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D13" s="15" t="inlineStr">
         <ns0:is>
-          <ns0:t>明确绕过该层的伤害不吸收；雷盾耗尽的同轮不接灵障；同轮原已启用灵障可继续承伤。</ns0:t>
+          <ns0:t>明确绕过该层的伤害不吸收；雷盾耗尽的同轮不接灵盾；同轮原已启用灵盾可继续承伤。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E13" s="15" t="inlineStr">
@@ -23360,17 +23360,17 @@
       </ns0:c>
       <ns0:c r="B14" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>普通灵障再生成</ns0:t>
+          <ns0:t>普通灵盾再生成</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C14" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>再次生成加进现有普通灵障池，实际增加不超过当前容量缺口；容量足够时10＋15＝25，溢出不存入。</ns0:t>
+          <ns0:t>再次生成加进现有普通灵盾池，实际增加不超过当前容量缺口；容量足够时10＋15＝25，溢出不存入。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D14" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>仅普通灵障；来源份额为返锋等合格效果保留，不能抹去来源。</ns0:t>
+          <ns0:t>仅普通灵盾；来源份额为返锋等合格效果保留，不能抹去来源。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E14" s="4" t="inlineStr">
@@ -23387,12 +23387,12 @@
       </ns0:c>
       <ns0:c r="B15" s="15" t="inlineStr">
         <ns0:is>
-          <ns0:t>普通灵障容量</ns0:t>
+          <ns0:t>普通灵盾容量</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C15" s="15" t="inlineStr">
         <ns0:is>
-          <ns0:t>当前普通灵障上限＝境界基础上限＋阵盘、法器及其他明确来源的上限加成。凡人10、炼气20、筑基30、结丹40、元婴50、化神60；上限加成暂不设统一封顶。池内存值仍受当前上限约束。</ns0:t>
+          <ns0:t>当前普通灵盾上限＝境界基础上限＋阵盘、法器及其他明确来源的上限加成。凡人10、炼气20、筑基30、结丹40、元婴50、化神60；上限加成暂不设统一封顶。池内存值仍受当前上限约束。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D15" s="15" t="inlineStr">
@@ -23414,7 +23414,7 @@
       </ns0:c>
       <ns0:c r="B16" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>普通灵障生命周期</ns0:t>
+          <ns0:t>普通灵盾生命周期</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C16" s="4" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </ns0:c>
       <ns0:c r="D16" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>普通灵障与特殊盾分别保存；不把雷盾生层／替换当普通灵障到期。</ns0:t>
+          <ns0:t>普通灵盾与特殊盾分别保存；不把雷盾生层／替换当普通灵盾到期。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E16" s="4" t="inlineStr">
@@ -23495,17 +23495,17 @@
       </ns0:c>
       <ns0:c r="B19" s="15" t="inlineStr">
         <ns0:is>
-          <ns0:t>灵障珠停用与CD重启</ns0:t>
+          <ns0:t>灵盾珠停用与CD重启</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C19" s="15" t="inlineStr">
         <ns0:is>
-          <ns0:t>F14灵障珠在普通灵障达到当前上限时立即停用，不发动、不扣灵力、不继续CD倒数，也不积累就绪资格。停用后，受到攻击使普通灵障值减少，才重新启用，并从完整10.5秒CD重新倒数；不继承停用前剩余CD，不在受击当刻立即补盾。CD完成且正常发动资格满足时，消耗6灵力，增加min(15,容量缺口)普通灵障；若因此达到上限，再次停用。此为本件专属停用条件，不等于受到【禁用】控制，也不自动推广其他法器。</ns0:t>
+          <ns0:t>F14灵盾珠在普通灵盾达到当前上限时立即停用，不发动、不扣灵力、不继续CD倒数，也不积累就绪资格。停用后，受到攻击使普通灵盾值减少，才重新启用，并从完整10.5秒CD重新倒数；不继承停用前剩余CD，不在受击当刻立即补盾。CD完成且正常发动资格满足时，消耗6灵力，增加min(15,容量缺口)普通灵盾；若因此达到上限，再次停用。此为本件专属停用条件，不等于受到【禁用】控制，也不自动推广其他法器。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D19" s="15" t="inlineStr">
         <ns0:is>
-          <ns0:t>只指普通灵障达到当前上限；受攻击实际减少普通灵障后重启。雷盾受损不等于普通灵障减少；本件自停不使用3秒【禁用】控制模板。</ns0:t>
+          <ns0:t>只指普通灵盾达到当前上限；受攻击实际减少普通灵盾后重启。雷盾受损不等于普通灵盾减少；本件自停不使用3秒【禁用】控制模板。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E19" s="15" t="inlineStr">
@@ -35137,7 +35137,7 @@
       </ns0:c>
       <ns0:c r="AB5" s="13" t="inlineStr">
         <ns0:is>
-          <ns0:t>普通灵障生成</ns0:t>
+          <ns0:t>普通灵盾生成</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AC5" s="13" t="inlineStr">
@@ -37182,7 +37182,7 @@
       </ns0:c>
       <ns0:c r="B23" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>灵障珠</ns0:t>
+          <ns0:t>灵盾珠</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C23" s="4" t="inlineStr">
@@ -37236,7 +37236,7 @@
       </ns0:c>
       <ns0:c r="Q23" s="4" t="inlineStr">
         <ns0:is>
-          <ns0:t>正常发动消耗灵力6／体力0／数量0；普通灵障满值停用，不发动不扣费；受攻击减值后重开完整10.5秒CD。</ns0:t>
+          <ns0:t>正常发动消耗灵力6／体力0／数量0；普通灵盾满值停用，不发动不扣费；受攻击减值后重开完整10.5秒CD。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R23" s="4" t="inlineStr">
@@ -37285,7 +37285,7 @@
       </ns0:c>
       <ns0:c r="AF23" s="14" t="inlineStr">
         <ns0:is>
-          <ns0:t>普通灵障＋15（受当前上限限制）；F14灵障珠在普通灵障达到当前上限时立即停用，不发动、不扣灵力、不继续CD倒数，也不积累就绪资格。停用后，受到攻击使普通灵障值减少，才重新启用，并从完整10.5秒CD重新倒数；不继承停用前剩余CD，不在受击当刻立即补盾。CD完成且正常发动资格满足时，消耗6灵力，增加min(15,容量缺口)普通灵障；若因此达到上限，再次停用。此为本件专属停用条件，不等于受到【禁用】控制，也不自动推广其他法器。</ns0:t>
+          <ns0:t>普通灵盾＋15（受当前上限限制）；F14灵盾珠在普通灵盾达到当前上限时立即停用，不发动、不扣灵力、不继续CD倒数，也不积累就绪资格。停用后，受到攻击使普通灵盾值减少，才重新启用，并从完整10.5秒CD重新倒数；不继承停用前剩余CD，不在受击当刻立即补盾。CD完成且正常发动资格满足时，消耗6灵力，增加min(15,容量缺口)普通灵盾；若因此达到上限，再次停用。此为本件专属停用条件，不等于受到【禁用】控制，也不自动推广其他法器。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG23" s="14" t="inlineStr">
